--- a/output/screener_output.xlsx
+++ b/output/screener_output.xlsx
@@ -435,1556 +435,1625 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="76" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>broad_sector</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>market_cap_crore</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>pb_ratio</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dividend_yield_pct</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>net_profit</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>sector_relative_score</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Interglobe Aviation Ltd</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" s="2" t="n">
         <v>892.5683060109289</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>24.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>11.8527226285847</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>22.61</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" s="2" t="n">
         <v>9424</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="K2" s="2" t="n">
         <v>19.31</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>120.69</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>121.24</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1040632.92</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>76.23</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>7.87</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>4.27</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>68904</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>8167</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>82.08</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>IRCTC</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="E3" s="2" t="n">
         <v>34.39628482972136</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>53.8</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>26.01873536299766</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>82.73999999999999</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J3" s="2" t="n">
         <v>667</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="K3" s="2" t="n">
         <v>17.96</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>29.17</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>28.47</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1258520.29</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>60.44</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>5.74</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>1.08</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4270</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>1111</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>81.45999999999999</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>98.72</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>ADANIPOWER</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Adani Power Ltd</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>48.27674122146251</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>32.2</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>41.36759945184802</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="J4" s="2" t="n">
         <v>17651</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>16.09</v>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
         <v>1372183.55</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>44.57</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>9.91</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>1.65</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>50351</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>20829</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>77.64</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Trent Ltd</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="E5" s="2" t="n">
         <v>36.30776794493609</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>23.8</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>11.93535353535353</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="J5" s="2" t="n">
         <v>841</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="K5" s="2" t="n">
         <v>36.31</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>73.11</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>69.52</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>571322.04</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>8.65</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>11.82</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>12375</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>1477</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>67.5</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>69.95</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Nestle India Ltd</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>117.7544910179641</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>185.43</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>16.12281708616873</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>41.19</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>2938</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="K6" s="2" t="n">
         <v>14.55</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>14.85</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>15.44</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1677775.19</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>54.96</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>14.34</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3.85</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>24394</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>3933</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>66.89</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>93.09</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Tata Consultancy Services Ltd</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>50.94431367348518</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>64.3</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>19.13671215020777</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>0.09</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="J7" s="2" t="n">
         <v>50429</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>10.46</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>7.87</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>461188.15</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>78.69</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>6.08</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>1.62</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>240893</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>46099</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>66.31</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>LTIM</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>LTIMindtree Ltd</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="E8" s="2" t="n">
         <v>22.9043860525527</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>34.1</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>12.90931103415266</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>31.93</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="J8" s="2" t="n">
         <v>1752</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="K8" s="2" t="n">
         <v>30.33</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>24.78</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>12.24</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1347046.9</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>64.52</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>2.38</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>4.43</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>35517</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>4585</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>66.31</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Asian Paints
 Indian Multi-National Paint and Coating Manufacturing Company</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>29.67748825288338</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>41.75</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>15.6585434568249</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.13</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>41</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="J9" s="2" t="n">
         <v>3556</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>13.03</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>20.28</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>20.97</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>2126725.18</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>73.37</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>3.9</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>2.42</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>35495</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>5558</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>64.06999999999999</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>96.19</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">Adani Ports &amp; Special Economic Zone Ltd
 </t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="E10" s="2" t="n">
         <v>15.3548827162833</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>12.9</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>30.33956048070083</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>5.95</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="J10" s="2" t="n">
         <v>8250</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="K10" s="2" t="n">
         <v>19.58</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>14.91</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>14.87</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>675598.01</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>48.9</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>2.31</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>1.16</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>26711</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>8104</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>63.31</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>80.09</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Infosys Ltd</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="E11" s="2" t="n">
         <v>29.78800671841663</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>40</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>17.08075746730006</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>0.09</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>87.52</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>20117</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="K11" s="2" t="n">
         <v>13.2</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>11.24</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>12.47</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>1112279.92</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>35.99</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>153670</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>26248</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>60.22</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>79.09999999999999</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Sun Pharmaceuticals Industries Ltd</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="E12" s="2" t="n">
         <v>15.09416181067115</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>17.3</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>19.81565870053818</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>58.33</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>11372</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="K12" s="2" t="n">
         <v>10.78</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>24.54</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>29.46</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1339586.09</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>37.9</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6.71</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>3.88</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>48497</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>9610</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>59.75</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>PIDILITIND</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Pidilite Industries Ltd</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="E13" s="2" t="n">
         <v>20.78030212917806</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>29.7</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>14.10805136073649</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>54.33</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="J13" s="2" t="n">
         <v>955</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="K13" s="2" t="n">
         <v>11.84</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>13.49</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>13.56</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>162274.18</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>36.12</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>12.3</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>1.01</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>12383</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>1747</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>56.96</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>77.51000000000001</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>HCL Technologies Ltd</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="E14" s="2" t="n">
         <v>23.01393141233172</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>29.6</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>14.29312274253273</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>0.08</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>46.46</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>15840</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="K14" s="2" t="n">
         <v>12.71</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>9.19</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>9.41</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>412593.29</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>63.63</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>5.44</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>1.99</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>109913</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>15710</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>56.49</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>66.3</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>ICICIGI</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>ICICI Lombard General Insurance Company Ltd</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="E15" s="2" t="n">
         <v>15.7230643179025</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>22.5</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>9.366915605017816</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>160.03</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>486</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="K15" s="2" t="n">
         <v>12.91</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>12.84</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>11.14</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>1271789.21</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>49</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>7.86</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>20487</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>1919</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>56.32</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>78.03</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Eicher Motors Ltd</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="E16" s="2" t="n">
         <v>22.17234691050152</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>31.1</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>24.19569424286405</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>114.71</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>890</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="K16" s="2" t="n">
         <v>11.04</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>12.68</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>12.51</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>222391.83</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>15.62</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>13.61</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>16536</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>4001</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>55.21</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>44.62</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Larsen &amp; Toubro Ltd</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>77.66510140873214</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>17.18</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>7.031246466738726</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>3.54</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>20445</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>10.34</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>8.76</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>8.56</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>1124597.5</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>30.8</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>2.48</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>1.26</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>221113</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>15547</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>53.08</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>62.42</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Dr Reddys Laboratories Ltd</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="E18" s="2" t="n">
         <v>19.74233736816026</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>26.5</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>19.9136053693192</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>51.71</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>509</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="K18" s="2" t="n">
         <v>12.64</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>23.39</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>23.84</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>2441803.28</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>11.73</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>10.19</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>0.09</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>28011</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>5578</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>49.29</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>ICICI Bank Ltd</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="E19" s="2" t="n">
         <v>17.99027109750765</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>7.6</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>28.8880112339828</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="H19" s="3" t="n">
         <v>6.45</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1.3</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>12547</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="K19" s="2" t="n">
         <v>17.25</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>51.95</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>55.18</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>1319221.86</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>25.76</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>6.2</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>3.43</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>159516</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>46081</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>48.45</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>59.33</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Maruti Suzuki India Ltd</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="E20" s="2" t="n">
         <v>15.75038535195478</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>23.67</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>9.50809964894472</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>117.91</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>4936</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="K20" s="2" t="n">
         <v>10.51</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>12.01</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>11.14</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>1503863.63</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>20.78</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>8.26</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>141858</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>13488</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>47.62</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>28.98</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>CANBK</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Canara Bank</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="E21" s="2" t="n">
         <v>16.71605179468811</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>6.63</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>13.93516047014541</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="H21" s="3" t="n">
         <v>14.87</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>1.61</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>13296</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="K21" s="2" t="n">
         <v>18.18</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>85.78</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>53.42</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>496415.88</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>36.74</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>12.61</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>3.81</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>110519</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>15401</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>39.79</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>38.76</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>HAVELLS</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Havells India Ltd</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="E22" s="2" t="n">
         <v>17.06727541291795</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>24.4</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>6.837009144701453</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>25.36</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="J22" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="K22" s="2" t="n">
         <v>13.04</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>10.03</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>9</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>2521508.87</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>45.41</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>14.08</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>18590</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>1271</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>39.79</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>39.45</v>
       </c>
     </row>
@@ -1999,471 +2068,492 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>broad_sector</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>market_cap_crore</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>pb_ratio</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dividend_yield_pct</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>net_profit</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>sector_relative_score</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>IRFC</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Indian Railway Finance Corporation Ltd</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>13.0380853616381</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>5.73</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>24.0645524488647</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="H2" s="3" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1.32</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>7906</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>19.07</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>23.25</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>20.11</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2618348.58</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>9.81</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>3.91</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>2.82</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>26645</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>6412</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>43.61</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>47.84</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>BANKBARODA</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Bank of Baroda</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>15.7618637908999</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>6.33</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>15.93948250956673</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>12.14</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1.9</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>-7559</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>17.48</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>74.51000000000001</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>55.18</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>590971.02</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="O3" s="2" t="n">
         <v>16.89</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="P3" s="2" t="n">
         <v>4.15</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>118379</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>18869</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>37.56</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>33.47</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mahindra &amp; Mahindra Ltd
 </t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>18.53754343556428</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>26.98</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>8.822387437265419</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>1.64</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>3.76</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>-11245</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>5.84</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>15.32</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>16.18</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>4173085.48</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>14.22</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="P4" s="2" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>2.37</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>139078</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>12270</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>34.63</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>2.21</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>MOTHERSON</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Samvardhana Motherson International Ltd</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>11.54654941693749</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>13.7</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>3.060025128683176</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.76</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>5.22</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>925</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>7.56</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>5.92</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>146151.16</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="O5" s="2" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>2.38</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>98692</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>3020</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>33.56</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>IndusInd Bank Ltd</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>14.25227319776422</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>7.93</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>19.56369677362945</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>6.89</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1.88</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>-17468</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>15.5</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>22.08</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>15.9</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1807433.12</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="O6" s="2" t="n">
         <v>8.99</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="P6" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>1.42</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>45748</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>8950</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>30.28</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>16.18</v>
       </c>
     </row>
@@ -2478,1422 +2568,1485 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="51" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>broad_sector</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>market_cap_crore</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>pb_ratio</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dividend_yield_pct</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>net_profit</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>sector_relative_score</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Interglobe Aviation Ltd</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>892.5683060109289</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>24.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>11.8527226285847</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>22.61</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>9424</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="K2" s="2" t="n">
         <v>19.31</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>120.69</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>121.24</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1040632.92</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>76.23</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>7.87</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>4.27</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>68904</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>8167</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>82.08</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>IRCTC</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>34.39628482972136</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>53.8</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>26.01873536299766</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>82.73999999999999</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>667</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="K3" s="2" t="n">
         <v>17.96</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>29.17</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>28.47</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1258520.29</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>60.44</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>5.74</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>1.08</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4270</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>1111</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>81.45999999999999</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>98.72</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Trent Ltd</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>36.30776794493609</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>23.8</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>11.93535353535353</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>841</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>36.31</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>73.11</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>69.52</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>571322.04</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>8.65</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>11.82</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>12375</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>1477</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>67.5</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>69.95</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>LTIM</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>LTIMindtree Ltd</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>22.9043860525527</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>34.1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>12.90931103415266</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>31.93</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1752</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="K5" s="2" t="n">
         <v>30.33</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>24.78</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>12.24</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1347046.9</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>64.52</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>2.38</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>4.43</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>35517</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>4585</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>66.31</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">Titan Company Ltd
 </t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>37.2192057915469</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>22.7</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>6.843630099444054</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>1.65</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>9.41</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1506</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="K6" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>20.27</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>19.51</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1793769.72</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>10.13</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>10.51</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>51084</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>3496</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>61.8</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>58.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>DMART</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Avenue Supermarts Ltd</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>13.56294790886726</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>19.4</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>4.993207190533383</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>73.29000000000001</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>278</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>20.48</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>22.97</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>22.74</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>3053088.97</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>72.53</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>11.71</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>50789</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>2536</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>52.34</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>38.71</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>ATGL</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Adani Total Gas Ltd</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>18.65921787709497</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>21.2</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>14.92737430167598</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>10.5</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" s="2" t="n">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>23.88</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>24.57</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1535602.41</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>56.96</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>5.76</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>0.51</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>4475</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>668</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>50.03</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>36.7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>ICICI Bank Ltd</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>17.99027109750765</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>7.6</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>28.8880112339828</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="H9" s="3" t="n">
         <v>6.45</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>1.3</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>12547</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>17.25</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>51.95</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>55.18</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>1319221.86</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>25.76</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>6.2</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>3.43</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>159516</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>46081</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>48.45</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>59.33</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Bajaj Finance Ltd</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>18.8419213518306</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>11.9</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>26.28792839991269</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>3.82</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>2689.17</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>-79931</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="K10" s="2" t="n">
         <v>24.35</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="L10" s="2" t="n">
         <v>29.32</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>27.56</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>2473271.58</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>69.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>4.11</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>0.27</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>54972</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>14451</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>48.01</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>58.29</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Adani Enterprises Ltd</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>8.534650424813185</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>11.6</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>3.458790097592848</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>2.75</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>-8455</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="K11" s="2" t="n">
         <v>19.02</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="L11" s="2" t="n">
         <v>45.81</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>31.95</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>187927.97</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>58.87</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>10.41</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>0.83</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>96421</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>3335</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>45.14</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>48.7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>HDFC Bank Ltd</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>14.33974005030719</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>7.67</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>23.07288232992184</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="H12" s="3" t="n">
         <v>6.81</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>1.4</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>35669</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="K12" s="2" t="n">
         <v>21.95</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="L12" s="2" t="n">
         <v>23.87</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>15.42</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>808359.03</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>49.42</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>4.4</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>4.33</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>283649</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>65446</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>44.09</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>48.98</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>IRFC</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Indian Railway Finance Corporation Ltd</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>13.0380853616381</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>5.73</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>24.0645524488647</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="H13" s="3" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>1.32</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>7906</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="K13" s="2" t="n">
         <v>19.07</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="L13" s="2" t="n">
         <v>23.25</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>20.11</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>2618348.58</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>9.81</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>3.91</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>2.82</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>26645</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>6412</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>43.61</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>47.84</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Bajaj Finserv Ltd</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>25.85035141227954</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>21.14</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>14.12820930948886</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="H14" s="3" t="n">
         <v>4.79</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>2.2</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>-79634</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="K14" s="2" t="n">
         <v>20.97</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>23.75</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>20.59</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1905112.17</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>15.07</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>6.08</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>2.56</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>110382</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>15595</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>40.3</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>39.98</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>CANBK</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Canara Bank</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>16.71605179468811</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>6.63</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>13.93516047014541</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="H15" s="3" t="n">
         <v>14.87</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>1.61</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>13296</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="K15" s="2" t="n">
         <v>18.18</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="L15" s="2" t="n">
         <v>85.78</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>53.42</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>496415.88</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>36.74</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>12.61</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>3.81</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>110519</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>15401</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>39.79</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>38.76</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>BANKBARODA</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Bank of Baroda</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>15.7618637908999</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>6.33</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>15.93948250956673</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="H16" s="3" t="n">
         <v>12.14</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>1.9</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>-7559</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="K16" s="2" t="n">
         <v>17.48</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>74.51000000000001</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>55.18</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>590971.02</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>16.89</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>4.15</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>118379</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>18869</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>37.56</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>33.47</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Tata Consumer Products Ltd</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>7.566793298872766</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>10.6</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>7.990266999868473</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>25.32</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>26</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>15.96</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>14.87</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>350543.35</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>54.79</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>7.14</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>15206</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>1215</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>37.36</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>21.54</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">Shriram Finance Ltd
 </t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>15.11635033812082</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>11.3</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>20.33362647026492</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="H18" s="3" t="n">
         <v>3.99</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>0.68</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>-31359</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="K18" s="2" t="n">
         <v>18.56</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="L18" s="2" t="n">
         <v>23.49</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>14.29</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>868933.47</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>68.53</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>7.91</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>36388</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>7399</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>35.43</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>28.41</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>CHOLAFIN</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Cholamandalam Investment &amp; Finance Company Ltd</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>17.45521359669269</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>10.4</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>17.84689244899024</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="H19" s="3" t="n">
         <v>6.86</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>21.21</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>-38538</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="K19" s="2" t="n">
         <v>21.94</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="L19" s="2" t="n">
         <v>23.36</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>22.28</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>971931.96</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>16.79</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>10.36</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>2.83</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>19163</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>3420</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>33.34</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>23.44</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>IndusInd Bank Ltd</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>14.25227319776422</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>7.93</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>19.56369677362945</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="H20" s="3" t="n">
         <v>6.89</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>1.88</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>-17468</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="K20" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="L20" s="2" t="n">
         <v>22.08</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>15.9</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>1807433.12</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>8.99</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>3.7</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>1.42</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>45748</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>8950</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>30.28</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>16.18</v>
       </c>
     </row>
@@ -3908,2300 +4061,2402 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="76" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>broad_sector</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>market_cap_crore</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>pb_ratio</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dividend_yield_pct</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>net_profit</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>sector_relative_score</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Interglobe Aviation Ltd</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>892.5683060109289</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>24.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>11.8527226285847</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>0.02</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>22.61</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" s="2" t="n">
         <v>9424</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>19.31</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>120.69</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>121.24</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1040632.92</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>76.23</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>7.87</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>4.27</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>68904</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>8167</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>82.08</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>HAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Hindustan Aeronautics Ltd</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>3816.582914572864</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>38.9</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>24.99917711727725</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.62</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>270.88</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J3" s="2" t="n">
         <v>1814</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>26.49</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>26.64</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2643616.86</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>71.89</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>3.65</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>2.77</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>30381</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>7595</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>74.83</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Trent Ltd</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>36.30776794493609</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>23.8</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>11.93535353535353</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>0.43</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="J4" s="2" t="n">
         <v>841</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>36.31</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>73.11</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>69.52</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>571322.04</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>8.65</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>11.82</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>12375</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>1477</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>67.5</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>69.95</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Nestle India Ltd</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>117.7544910179641</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>185.43</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>16.12281708616873</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.1</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>41.19</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="J5" s="2" t="n">
         <v>2938</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>14.55</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>14.85</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>15.44</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1677775.19</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>54.96</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>14.34</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>24394</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>3933</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>66.89</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>93.09</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>LTIM</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>LTIMindtree Ltd</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>22.9043860525527</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>34.1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>12.90931103415266</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.1</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>31.93</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>1752</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>30.33</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>24.78</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>12.24</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1347046.9</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>64.52</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2.38</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>4.43</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>35517</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>4585</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>66.31</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">ITC Ltd
 </t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>27.85107439569436</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>34.76</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>29.28202523071713</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>362.96</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="J7" s="2" t="n">
         <v>18742</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>7.95</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>10.08</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>332245.58</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>47.85</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>3.24</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>70866</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>20751</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>90.5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>BAJAJHLDNG</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Bajaj Holdings &amp; Investment Ltd</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>13.57678765646027</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>13.1</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>432.7262044653349</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>3764.5</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="J8" s="2" t="n">
         <v>1469</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>31.61</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>19.3</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>18.97</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2191568.13</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>37.73</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>3.37</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>1702</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>7365</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>65.56999999999999</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Coal India Ltd</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>45.16982956605826</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>63.6</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>26.25628846856468</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>0.08</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>11.24</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="J9" s="2" t="n">
         <v>13617</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>16.43</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>16.85</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>454024.84</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>34.27</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>14.75</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>4.38</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>142324</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>37369</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>65.52</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Asian Paints
 Indian Multi-National Paint and Coating Manufacturing Company</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>29.67748825288338</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>41.75</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>15.6585434568249</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>0.13</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>41</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="J10" s="2" t="n">
         <v>3556</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>13.03</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>20.28</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>20.97</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>2126725.18</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>73.37</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>3.9</v>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>35495</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>5558</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>64.06999999999999</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>96.19</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>LICI</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Life Insurance Corporation of India</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>49.44710986501021</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>63.79</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>4.836600998148862</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>371.94</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>853</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>8.16</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>73.18000000000001</v>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
         <v>183583.67</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>30.67</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>8.1</v>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="Q11" s="2" t="n">
         <v>3.77</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>845966</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>40916</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>63.14</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>94.23</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">Titan Company Ltd
 </t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>37.2192057915469</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>22.7</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>6.843630099444054</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>1.65</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>9.41</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>1506</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>20.9</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>20.27</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>19.51</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1793769.72</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>10.13</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>10.51</v>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>51084</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>3496</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>61.8</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>58.2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Infosys Ltd</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>29.78800671841663</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>40</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>17.08075746730006</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>0.09</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>87.52</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="J13" s="2" t="n">
         <v>20117</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>13.2</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>11.24</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>12.47</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1112279.92</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>35.99</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="Q13" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>153670</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>26248</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>60.22</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>79.09999999999999</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Bajaj Auto Ltd</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>26.61418410330778</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>33.5</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>17.17851571205706</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>174.42</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>6486</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>10.18</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>653817.3</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>29.91</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>9.83</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="Q14" s="2" t="n">
         <v>3.59</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>44870</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>7708</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>60.09</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>54.68</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Sun Pharmaceuticals Industries Ltd</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>15.09416181067115</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>17.3</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>19.81565870053818</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>0.05</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>58.33</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>11372</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>10.78</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>24.54</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>29.46</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>1339586.09</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>37.9</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>6.71</v>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="Q15" s="2" t="n">
         <v>3.88</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>48497</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>9610</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>59.75</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>ICICIGI</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>ICICI Lombard General Insurance Company Ltd</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>15.7230643179025</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>22.5</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>9.366915605017816</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>160.03</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>486</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>12.91</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>12.84</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>11.14</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>1271789.21</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>49</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>7.86</v>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="Q16" s="2" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>20487</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>1919</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>56.32</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>78.03</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Eicher Motors Ltd</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>22.17234691050152</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>31.1</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>24.19569424286405</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>0.02</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>114.71</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>890</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>11.04</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>12.68</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>12.51</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>222391.83</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>15.62</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>13.61</v>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="Q17" s="2" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>16536</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>4001</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>55.21</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>44.62</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Power Grid Corporation of India Ltd</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>17.87001124549607</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>13.2</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>33.97028990249329</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>1.42</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>4.6</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>24176</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>5.51</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>9.19</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>9.1</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>372584.24</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>64.39</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>5.1</v>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="Q18" s="2" t="n">
         <v>3.09</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>45843</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>15573</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>53.95</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>45.69</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Jio Financial Services Ltd</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>1.153456416595399</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>2.16</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>86.52291105121293</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>198.8</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>763</v>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
         <v>1401774.99</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>34.24</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>9.91</v>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>3.09</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>1855</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>1605</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>52.42</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>68.76000000000001</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t xml:space="preserve">Hindustan Unilever Ltd
 </t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>20.07497364207896</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>27.2</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>16.61173581491534</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>0.03</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>57.85</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>10145</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>9.5</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>11.15</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>548890.59</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>34.51</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>11.88</v>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="Q20" s="2" t="n">
         <v>4.32</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>61896</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>10282</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>52.05</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>57.14</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>TATAMOTORS</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Tata Motors Ltd</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>37.45613415294755</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>20.1</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>7.263066074788551</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>1.26</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>6.53</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>45133</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>7.72</v>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
         <v>1504106.64</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>67.06999999999999</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>0.93</v>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>437928</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>31807</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>51.7</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>37.39</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Apollo Hospitals
 Chain of Indian private hospitals</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>13.48039215686275</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>17.2</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>4.905818773282963</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>0.77</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>5.57</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="J22" s="2" t="n">
         <v>383</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>14.66</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>36.13</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>29.95</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>1905622.43</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>47.72</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>7.68</v>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="Q22" s="2" t="n">
         <v>3.22</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>19059</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>935</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>50.93</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>15.68</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>ICICI Bank Ltd</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>17.99027109750765</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>7.6</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>28.8880112339828</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>6.45</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>1.3</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="J23" s="2" t="n">
         <v>12547</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>17.25</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>51.95</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>55.18</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>1319221.86</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>25.76</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>6.2</v>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="Q23" s="2" t="n">
         <v>3.43</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>159516</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>46081</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>48.45</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>59.33</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>HDFC Bank Ltd</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>14.33974005030719</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>7.67</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>23.07288232992184</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>6.81</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>1.4</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="J24" s="2" t="n">
         <v>35669</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>21.95</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>23.87</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>15.42</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>808359.03</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>49.42</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>4.4</v>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="Q24" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>283649</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>65446</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>44.09</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>48.98</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>IRFC</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Indian Railway Finance Corporation Ltd</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>13.0380853616381</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>5.73</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>24.0645524488647</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>1.32</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="J25" s="2" t="n">
         <v>7906</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>19.07</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>23.25</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>20.11</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>2618348.58</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>9.81</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>3.91</v>
       </c>
-      <c r="P25" s="2" t="n">
+      <c r="Q25" s="2" t="n">
         <v>2.82</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>26645</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>6412</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>43.61</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>47.84</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>BOSCHLTD</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Bosch Ltd</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>20.63992042440318</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>20.6</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>14.88611227356968</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>71.78</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="J26" s="2" t="n">
         <v>1536</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>6.72</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>9.26</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>2599556.05</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>58.43</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>6.47</v>
       </c>
-      <c r="P26" s="2" t="n">
+      <c r="Q26" s="2" t="n">
         <v>4.23</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>16727</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>2490</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>40.05</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>13.38</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>CANBK</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Canara Bank</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>16.71605179468811</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>6.63</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>13.93516047014541</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>14.87</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>1.61</v>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="J27" s="2" t="n">
         <v>13296</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>18.18</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>85.78</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>53.42</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>496415.88</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>36.74</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>12.61</v>
       </c>
-      <c r="P27" s="2" t="n">
+      <c r="Q27" s="2" t="n">
         <v>3.81</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>110519</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>15401</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>39.79</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>38.76</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>HAVELLS</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Havells India Ltd</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>17.06727541291795</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>24.4</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>6.837009144701453</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>0.04</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>25.36</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="J28" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>13.04</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10.03</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>9</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2521508.87</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>45.41</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>14.08</v>
       </c>
-      <c r="P28" s="2" t="n">
+      <c r="Q28" s="2" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>18590</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>1271</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>39.79</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>39.45</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>SHREECEM</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Shree Cement Ltd</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>8.370767521615225</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>14.8</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>8.445007553238145</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>0.08</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>19.83</v>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="J29" s="2" t="n">
         <v>1929</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>10.33</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>11.29</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>10.68</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>3154358.33</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>25.87</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>1.21</v>
       </c>
-      <c r="P29" s="2" t="n">
+      <c r="Q29" s="2" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>20521</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>1733</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>39.03</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>30.4</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t xml:space="preserve">Reliance Industries Ltd
 </t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>9.958650553699458</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>8.789365557299389</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>0.58</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>7.73</v>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="J30" s="2" t="n">
         <v>45207</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>14.68</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>11.95</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>432472.71</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>58.34</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>3.25</v>
       </c>
-      <c r="P30" s="2" t="n">
+      <c r="Q30" s="2" t="n">
         <v>4.21</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>899041</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>79020</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>38.97</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>11.35</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>DABUR</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Dabur India Ltd</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>18.35596999797284</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>22.3</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>14.60012899064818</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>0.14</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>23.24</v>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="J31" s="2" t="n">
         <v>1042</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>7.81</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>4.6</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>4.56</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>56521.84</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>50.95</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>13.59</v>
       </c>
-      <c r="P31" s="2" t="n">
+      <c r="Q31" s="2" t="n">
         <v>3.42</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>12404</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>1811</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>37.71</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>22.39</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>DLF</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>DLF Ltd</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>6.908270142781061</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>5.74</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>42.38369379181578</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>0.12</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>7.46</v>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="J32" s="2" t="n">
         <v>1010</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>-5.14</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>15.7</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>12.89</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>1381712.03</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>46.26</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>14.32</v>
       </c>
-      <c r="P32" s="2" t="n">
+      <c r="Q32" s="2" t="n">
         <v>2.58</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>6427</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>2724</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>35.76</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>MOTHERSON</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Samvardhana Motherson International Ltd</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>11.54654941693749</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>13.7</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>3.060025128683176</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>0.76</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>5.22</v>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="J33" s="2" t="n">
         <v>925</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>7.56</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>5.92</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>146151.16</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>2.38</v>
       </c>
-      <c r="P33" s="2" t="n">
+      <c r="Q33" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>98692</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>3020</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>33.56</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6216,1553 +6471,1622 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>broad_sector</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>market_cap_crore</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>pb_ratio</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dividend_yield_pct</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>net_profit</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>sector_relative_score</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t xml:space="preserve">ITC Ltd
 </t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" s="2" t="n">
         <v>27.85107439569436</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>34.76</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>29.28202523071713</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>362.96</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>18742</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>7.95</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>10.08</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>332245.58</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>47.85</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>3.24</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>70866</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>20751</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>90.5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>LICI</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Life Insurance Corporation of India</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="E3" s="2" t="n">
         <v>49.44710986501021</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>63.79</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>4.836600998148862</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>371.94</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>853</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>8.16</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>73.18000000000001</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
         <v>183583.67</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>30.67</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8.1</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>3.77</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>845966</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>40916</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>63.14</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>94.23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>ICICIGI</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>ICICI Lombard General Insurance Company Ltd</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>15.7230643179025</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>22.5</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>9.366915605017816</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>160.03</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>486</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>12.91</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>12.84</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>11.14</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1271789.21</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>49</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7.86</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>20487</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>1919</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>56.32</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>78.03</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>ICICI Bank Ltd</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="E5" s="2" t="n">
         <v>17.99027109750765</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>7.6</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>28.8880112339828</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>6.45</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1.3</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>12547</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>17.25</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>51.95</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>55.18</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1319221.86</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>25.76</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>6.2</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3.43</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>159516</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>46081</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>48.45</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>59.33</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Bajaj Finance Ltd</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>18.8419213518306</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>11.9</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>26.28792839991269</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>3.82</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>2689.17</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>-79931</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>24.35</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>29.32</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>27.56</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2473271.58</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>69.2</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>4.11</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>0.27</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>54972</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>14451</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>48.01</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>58.29</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Maruti Suzuki India Ltd</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>15.75038535195478</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>23.67</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>9.50809964894472</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>117.91</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>4936</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>10.51</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>12.01</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>11.14</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1503863.63</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>20.78</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>8.26</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>141858</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>13488</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>47.62</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>28.98</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>SBI Life Insurance Company Ltd</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="E8" s="2" t="n">
         <v>12.70458814059566</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>13.2</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1.434978937479165</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>240.33</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>-2099</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>24.23</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>7.37</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>7.89</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>886097.71</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>69.98</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>9.48</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>1.62</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>131988</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>1894</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>46.96</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>55.8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">Kotak Mahindra Bank Ltd
 </t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>14.01301818853291</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>7.86</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>32.38615146611662</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="H9" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>1.24</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>6766</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>13.52</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>20.38</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>19.34</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>430223.52</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>32.9</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1.15</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>1.51</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>56237</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>18213</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>45.27</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>51.78</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>HDFC Bank Ltd</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="E10" s="2" t="n">
         <v>14.33974005030719</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>7.67</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>23.07288232992184</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>6.81</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>1.4</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>35669</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>21.95</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>23.87</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>15.42</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>808359.03</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>49.42</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>4.4</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>4.33</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>283649</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>65446</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>44.09</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>48.98</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>IRFC</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Indian Railway Finance Corporation Ltd</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="E11" s="2" t="n">
         <v>13.0380853616381</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>5.73</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>24.0645524488647</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="H11" s="3" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>1.32</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>7906</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>19.07</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>23.25</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>20.11</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>2618348.58</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>9.81</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>3.91</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>2.82</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>26645</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>6412</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>43.61</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>47.84</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>PNB</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Punjab National Bank</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="E12" s="2" t="n">
         <v>61.32056519118731</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>1.63</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>8.395910695456838</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="H12" s="3" t="n">
         <v>3.68</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="n">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
         <v>-29445</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>15.9</v>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
         <v>1825925.6</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>19.29</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>10.91</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>1.32</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>109065</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>9157</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>43.41</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>47.36</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Bajaj Finserv Ltd</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="E13" s="2" t="n">
         <v>25.85035141227954</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>21.14</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>14.12820930948886</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="H13" s="3" t="n">
         <v>4.79</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>2.2</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-79634</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>20.97</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>23.75</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>20.59</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1905112.17</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>15.07</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>6.08</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>2.56</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>110382</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>15595</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>40.3</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>39.98</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>BOSCHLTD</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Bosch Ltd</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="E14" s="2" t="n">
         <v>20.63992042440318</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>20.6</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>14.88611227356968</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>71.78</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1536</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>6.72</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>9.26</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>2599556.05</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>58.43</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>6.47</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>4.23</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>16727</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>2490</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>40.05</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>13.38</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>CANBK</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Canara Bank</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="E15" s="2" t="n">
         <v>16.71605179468811</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>6.63</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>13.93516047014541</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="H15" s="3" t="n">
         <v>14.87</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>1.61</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>13296</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>18.18</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>85.78</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>53.42</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>496415.88</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>36.74</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>12.61</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>3.81</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>110519</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>15401</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>39.79</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>38.76</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Axis Bank Ltd</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="E16" s="2" t="n">
         <v>15.83271240518905</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>7.06</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>22.73130411725443</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="H16" s="3" t="n">
         <v>8.25</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>1.69</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>-14556</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>14.74</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>39.67</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>35.1</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>948868.63</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>38.14</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>4.66</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>2.32</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>109369</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>24861</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>38.83</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>36.48</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>BANKBARODA</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Bank of Baroda</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>15.7618637908999</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>6.33</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>15.93948250956673</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="H17" s="3" t="n">
         <v>12.14</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>1.9</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-7559</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>17.48</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>74.51000000000001</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>55.18</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>590971.02</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>16.89</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>4.15</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>118379</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>18869</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>37.56</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>33.47</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">Shriram Finance Ltd
 </t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="E18" s="2" t="n">
         <v>15.11635033812082</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>11.3</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>20.33362647026492</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="H18" s="3" t="n">
         <v>3.99</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>0.68</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>-31359</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>18.56</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>23.49</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>14.29</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>868933.47</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>68.53</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>7.91</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>36388</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>7399</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>35.43</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>28.41</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>CHOLAFIN</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Cholamandalam Investment &amp; Finance Company Ltd</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="E19" s="2" t="n">
         <v>17.45521359669269</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>10.4</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>17.84689244899024</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="H19" s="3" t="n">
         <v>6.86</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>21.21</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>-38538</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>21.94</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>23.36</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>22.28</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>971931.96</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>16.79</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>10.36</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>2.83</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>19163</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>3420</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>33.34</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>23.44</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>RECLTD</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>REC Ltd</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="E20" s="2" t="n">
         <v>20.39653929343908</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>10</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>29.7682934528695</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="H20" s="3" t="n">
         <v>6.42</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>1.6</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>-59554</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>13.34</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>19.76</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>19.67</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>291917.42</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>31.49</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>4.59</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>2.18</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>47517</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>14145</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>32.41</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>21.24</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>PFC</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Power Finance Corporation Ltd</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="E21" s="2" t="n">
         <v>26.1609340860332</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>28.91659745596014</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="H21" s="3" t="n">
         <v>8.52</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>0.58</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>-101229</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>11.08</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>15.92</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>14.87</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>2011885.81</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>35.6</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>6.59</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>0.42</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>91508</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>26461</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>31.77</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>19.71</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>IndusInd Bank Ltd</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="E22" s="2" t="n">
         <v>14.25227319776422</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>7.93</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>19.56369677362945</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="H22" s="3" t="n">
         <v>6.89</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>1.88</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-17468</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>15.5</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>22.08</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>15.9</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>1807433.12</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>8.99</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>3.7</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>1.42</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>45748</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>8950</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>30.28</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>16.18</v>
       </c>
     </row>
